--- a/data/trans_dic/P16A_2_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,26; 35,81</t>
+          <t>23,39; 35,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,89; 48,81</t>
+          <t>39,12; 48,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,97; 40,09</t>
+          <t>32,6; 40,24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 26,4</t>
+          <t>18,49; 26,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 44,12</t>
+          <t>36,64; 43,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,33; 34,62</t>
+          <t>28,21; 34,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 33,38</t>
+          <t>23,35; 33,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 46,28</t>
+          <t>37,25; 46,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,63</t>
+          <t>31,95; 38,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 37,37</t>
+          <t>24,7; 37,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 44,02</t>
+          <t>20,05; 43,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,48; 38,48</t>
+          <t>23,65; 38,33</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,38; 28,41</t>
+          <t>18,07; 28,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 39,66</t>
+          <t>16,4; 39,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 32,36</t>
+          <t>18,84; 32,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 34,14</t>
+          <t>24,53; 34,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,26; 48,16</t>
+          <t>38,1; 48,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,21</t>
+          <t>32,3; 39,36</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,62; 31,17</t>
+          <t>22,5; 31,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,4; 75,47</t>
+          <t>39,37; 77,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,93; 65,56</t>
+          <t>32,61; 63,64</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 14,35</t>
+          <t>4,83; 14,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,64; 33,62</t>
+          <t>27,69; 33,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,03; 22,72</t>
+          <t>11,71; 22,94</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,17; 24,48</t>
+          <t>17,33; 24,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,85; 52,44</t>
+          <t>36,94; 52,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,71; 38,45</t>
+          <t>28,84; 37,7</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72442; 111527</t>
+          <t>72832; 110461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112647; 141372</t>
+          <t>113308; 141176</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192158; 240977</t>
+          <t>195929; 241844</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94353; 136832</t>
+          <t>95867; 138103</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187304; 227199</t>
+          <t>188674; 224786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>292750; 357708</t>
+          <t>291561; 352569</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75362; 105498</t>
+          <t>73798; 107228</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130163; 161585</t>
+          <t>130058; 161027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214463; 256989</t>
+          <t>212503; 258263</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76340; 116789</t>
+          <t>77197; 117054</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97614; 209430</t>
+          <t>95377; 208940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192996; 303331</t>
+          <t>186450; 302107</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32845; 50783</t>
+          <t>32297; 50210</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41700; 102631</t>
+          <t>42450; 103285</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82349; 141578</t>
+          <t>82447; 142941</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66300; 92050</t>
+          <t>66137; 92584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>98361; 123803</t>
+          <t>97932; 123691</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170246; 206528</t>
+          <t>170129; 207301</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>141199; 194558</t>
+          <t>140484; 193664</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>334625; 640917</t>
+          <t>334375; 658549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>485308; 966043</t>
+          <t>480464; 937810</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39996; 133299</t>
+          <t>44895; 133373</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198347; 241324</t>
+          <t>198708; 241061</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>197986; 374088</t>
+          <t>192780; 377735</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>594040; 847131</t>
+          <t>599658; 852926</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1367959; 1946538</t>
+          <t>1371287; 1936484</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2059043; 2757995</t>
+          <t>2068179; 2703878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_2_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 35,47</t>
+          <t>24,84; 35,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,12; 48,74</t>
+          <t>38,55; 47,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 40,24</t>
+          <t>32,54; 39,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 26,64</t>
+          <t>18,7; 27,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,64; 43,65</t>
+          <t>35,71; 43,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,21; 34,12</t>
+          <t>28,14; 34,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 33,93</t>
+          <t>24,35; 34,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,25; 46,12</t>
+          <t>38,19; 46,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 38,83</t>
+          <t>32,7; 39,36</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,7; 37,45</t>
+          <t>23,21; 35,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 43,92</t>
+          <t>38,85; 47,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 38,33</t>
+          <t>33,06; 40,72</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,07; 28,09</t>
+          <t>16,82; 26,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,4; 39,91</t>
+          <t>32,66; 41,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 32,67</t>
+          <t>26,47; 33,08</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,53; 34,34</t>
+          <t>23,64; 32,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,1; 48,12</t>
+          <t>37,71; 47,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,3; 39,36</t>
+          <t>31,86; 38,59</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,5; 31,02</t>
+          <t>23,02; 30,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,37; 77,54</t>
+          <t>36,82; 43,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,61; 63,64</t>
+          <t>31,39; 36,14</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 14,36</t>
+          <t>10,91; 15,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,69; 33,59</t>
+          <t>27,1; 32,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,71; 22,94</t>
+          <t>19,78; 23,46</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,33; 24,65</t>
+          <t>21,95; 25,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,94; 52,16</t>
+          <t>37,21; 39,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,84; 37,7</t>
+          <t>30,12; 32,29</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90052</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>127327</t>
+          <t>136010</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217380</t>
+          <t>229504</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72832; 110461</t>
+          <t>79208; 112668</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113308; 141176</t>
+          <t>121828; 149694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>195929; 241844</t>
+          <t>206578; 251518</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>115416</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>207405</t>
+          <t>215600</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>322821</t>
+          <t>334449</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95867; 138103</t>
+          <t>99225; 144034</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>188674; 224786</t>
+          <t>195164; 235422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>291561; 352569</t>
+          <t>303055; 367243</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>91576</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>150577</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234897</t>
+          <t>242153</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73798; 107228</t>
+          <t>76950; 108343</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130058; 161027</t>
+          <t>136090; 166926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212503; 258263</t>
+          <t>219847; 264621</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95148</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>164857</t>
+          <t>181928</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260005</t>
+          <t>291576</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77197; 117054</t>
+          <t>86621; 133147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95377; 208940</t>
+          <t>163948; 201812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>186450; 302107</t>
+          <t>262831; 323780</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80539</t>
+          <t>84030</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121674</t>
+          <t>127909</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32297; 50210</t>
+          <t>34595; 53887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42450; 103285</t>
+          <t>74754; 94412</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82447; 142941</t>
+          <t>115021; 143760</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>76355</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>110374</t>
+          <t>112564</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188919</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66137; 92584</t>
+          <t>64009; 88787</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97932; 123691</t>
+          <t>99464; 125425</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170129; 207301</t>
+          <t>170292; 206234</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>164916</t>
+          <t>190420</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>466963</t>
+          <t>311294</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631879</t>
+          <t>501714</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>140484; 193664</t>
+          <t>165663; 220064</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>334375; 658549</t>
+          <t>284270; 334413</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480464; 937810</t>
+          <t>468238; 539109</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>219175</t>
+          <t>247637</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>311607</t>
+          <t>351451</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44895; 133373</t>
+          <t>87051; 124989</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198708; 241061</t>
+          <t>225292; 272553</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>192780; 377735</t>
+          <t>322253; 382323</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>599658; 852926</t>
+          <t>775545; 887853</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1371287; 1936484</t>
+          <t>1390477; 1492474</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2068179; 2703878</t>
+          <t>2189604; 2347341</t>
         </is>
       </c>
     </row>
